--- a/tests/expedite-zmrp.xlsx
+++ b/tests/expedite-zmrp.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BA12"/>
+  <dimension ref="A1:BA16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2014,9 +2014,653 @@
         <v>24.07.2026</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>EXP-DRY-OLD</v>
+      </c>
+      <c r="B13" t="str">
+        <v>פריט EXP-DRY-OLD</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Test EXP-DRY-OLD</v>
+      </c>
+      <c r="D13" t="str">
+        <v>ספק א</v>
+      </c>
+      <c r="E13" t="str">
+        <v>01</v>
+      </c>
+      <c r="F13" t="str">
+        <v>פעיל</v>
+      </c>
+      <c r="G13" t="str">
+        <v>ND</v>
+      </c>
+      <c r="H13" t="str">
+        <v>A</v>
+      </c>
+      <c r="I13">
+        <v>95</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>30</v>
+      </c>
+      <c r="M13">
+        <v>2</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>100</v>
+      </c>
+      <c r="P13" t="str">
+        <v>USD</v>
+      </c>
+      <c r="Q13">
+        <v>100</v>
+      </c>
+      <c r="R13">
+        <v>100</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>5</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13" t="str">
+        <v>Z004</v>
+      </c>
+      <c r="Y13" t="str">
+        <v>מנוע</v>
+      </c>
+      <c r="Z13" t="str">
+        <v>ZT</v>
+      </c>
+      <c r="AA13" t="str">
+        <v>מתכנן</v>
+      </c>
+      <c r="AB13" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="str">
+        <v>שיווק</v>
+      </c>
+      <c r="AD13" t="str">
+        <v>מערכת</v>
+      </c>
+      <c r="AE13" t="str">
+        <v>100</v>
+      </c>
+      <c r="AF13" t="str">
+        <v>ZT</v>
+      </c>
+      <c r="AG13" t="str">
+        <v>200</v>
+      </c>
+      <c r="AH13" t="str">
+        <v>דגם</v>
+      </c>
+      <c r="AI13" t="str">
+        <v>300</v>
+      </c>
+      <c r="AJ13" t="str">
+        <v>מערכת</v>
+      </c>
+      <c r="AK13">
+        <v>110</v>
+      </c>
+      <c r="AL13">
+        <v>110</v>
+      </c>
+      <c r="AM13">
+        <v>110</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>10</v>
+      </c>
+      <c r="AP13">
+        <v>10</v>
+      </c>
+      <c r="AQ13">
+        <v>10</v>
+      </c>
+      <c r="AR13">
+        <v>10</v>
+      </c>
+      <c r="AS13">
+        <v>10</v>
+      </c>
+      <c r="AT13">
+        <v>10</v>
+      </c>
+      <c r="AU13">
+        <v>10</v>
+      </c>
+      <c r="AV13">
+        <v>10</v>
+      </c>
+      <c r="AW13">
+        <v>10</v>
+      </c>
+      <c r="AX13">
+        <v>10</v>
+      </c>
+      <c r="AY13">
+        <v>10</v>
+      </c>
+      <c r="AZ13" t="str">
+        <v>12.09.2026</v>
+      </c>
+      <c r="BA13" t="str">
+        <v>05.04.2024</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>EXP-DRY-MID</v>
+      </c>
+      <c r="B14" t="str">
+        <v>פריט EXP-DRY-MID</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Test EXP-DRY-MID</v>
+      </c>
+      <c r="D14" t="str">
+        <v>ספק א</v>
+      </c>
+      <c r="E14" t="str">
+        <v>01</v>
+      </c>
+      <c r="F14" t="str">
+        <v>פעיל</v>
+      </c>
+      <c r="G14" t="str">
+        <v>ND</v>
+      </c>
+      <c r="H14" t="str">
+        <v>A</v>
+      </c>
+      <c r="I14">
+        <v>95</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>30</v>
+      </c>
+      <c r="M14">
+        <v>2</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>100</v>
+      </c>
+      <c r="P14" t="str">
+        <v>USD</v>
+      </c>
+      <c r="Q14">
+        <v>100</v>
+      </c>
+      <c r="R14">
+        <v>100</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>5</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14" t="str">
+        <v>Z004</v>
+      </c>
+      <c r="Y14" t="str">
+        <v>מנוע</v>
+      </c>
+      <c r="Z14" t="str">
+        <v>ZT</v>
+      </c>
+      <c r="AA14" t="str">
+        <v>מתכנן</v>
+      </c>
+      <c r="AB14" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="str">
+        <v>שיווק</v>
+      </c>
+      <c r="AD14" t="str">
+        <v>מערכת</v>
+      </c>
+      <c r="AE14" t="str">
+        <v>100</v>
+      </c>
+      <c r="AF14" t="str">
+        <v>ZT</v>
+      </c>
+      <c r="AG14" t="str">
+        <v>200</v>
+      </c>
+      <c r="AH14" t="str">
+        <v>דגם</v>
+      </c>
+      <c r="AI14" t="str">
+        <v>300</v>
+      </c>
+      <c r="AJ14" t="str">
+        <v>מערכת</v>
+      </c>
+      <c r="AK14">
+        <v>110</v>
+      </c>
+      <c r="AL14">
+        <v>110</v>
+      </c>
+      <c r="AM14">
+        <v>110</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>10</v>
+      </c>
+      <c r="AP14">
+        <v>10</v>
+      </c>
+      <c r="AQ14">
+        <v>10</v>
+      </c>
+      <c r="AR14">
+        <v>10</v>
+      </c>
+      <c r="AS14">
+        <v>10</v>
+      </c>
+      <c r="AT14">
+        <v>10</v>
+      </c>
+      <c r="AU14">
+        <v>10</v>
+      </c>
+      <c r="AV14">
+        <v>10</v>
+      </c>
+      <c r="AW14">
+        <v>10</v>
+      </c>
+      <c r="AX14">
+        <v>10</v>
+      </c>
+      <c r="AY14">
+        <v>10</v>
+      </c>
+      <c r="AZ14" t="str">
+        <v>12.09.2026</v>
+      </c>
+      <c r="BA14" t="str">
+        <v>06.03.2026</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>EXP-DRY-NONE</v>
+      </c>
+      <c r="B15" t="str">
+        <v>פריט EXP-DRY-NONE</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Test EXP-DRY-NONE</v>
+      </c>
+      <c r="D15" t="str">
+        <v>ספק א</v>
+      </c>
+      <c r="E15" t="str">
+        <v>01</v>
+      </c>
+      <c r="F15" t="str">
+        <v>פעיל</v>
+      </c>
+      <c r="G15" t="str">
+        <v>ND</v>
+      </c>
+      <c r="H15" t="str">
+        <v>A</v>
+      </c>
+      <c r="I15">
+        <v>95</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>30</v>
+      </c>
+      <c r="M15">
+        <v>2</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>100</v>
+      </c>
+      <c r="P15" t="str">
+        <v>USD</v>
+      </c>
+      <c r="Q15">
+        <v>100</v>
+      </c>
+      <c r="R15">
+        <v>100</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>5</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15" t="str">
+        <v>Z004</v>
+      </c>
+      <c r="Y15" t="str">
+        <v>מנוע</v>
+      </c>
+      <c r="Z15" t="str">
+        <v>ZT</v>
+      </c>
+      <c r="AA15" t="str">
+        <v>מתכנן</v>
+      </c>
+      <c r="AB15" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="str">
+        <v>שיווק</v>
+      </c>
+      <c r="AD15" t="str">
+        <v>מערכת</v>
+      </c>
+      <c r="AE15" t="str">
+        <v>100</v>
+      </c>
+      <c r="AF15" t="str">
+        <v>ZT</v>
+      </c>
+      <c r="AG15" t="str">
+        <v>200</v>
+      </c>
+      <c r="AH15" t="str">
+        <v>דגם</v>
+      </c>
+      <c r="AI15" t="str">
+        <v>300</v>
+      </c>
+      <c r="AJ15" t="str">
+        <v>מערכת</v>
+      </c>
+      <c r="AK15">
+        <v>110</v>
+      </c>
+      <c r="AL15">
+        <v>110</v>
+      </c>
+      <c r="AM15">
+        <v>110</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>10</v>
+      </c>
+      <c r="AP15">
+        <v>10</v>
+      </c>
+      <c r="AQ15">
+        <v>10</v>
+      </c>
+      <c r="AR15">
+        <v>10</v>
+      </c>
+      <c r="AS15">
+        <v>10</v>
+      </c>
+      <c r="AT15">
+        <v>10</v>
+      </c>
+      <c r="AU15">
+        <v>10</v>
+      </c>
+      <c r="AV15">
+        <v>10</v>
+      </c>
+      <c r="AW15">
+        <v>10</v>
+      </c>
+      <c r="AX15">
+        <v>10</v>
+      </c>
+      <c r="AY15">
+        <v>10</v>
+      </c>
+      <c r="AZ15" t="str">
+        <v>12.09.2026</v>
+      </c>
+      <c r="BA15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>EXP-FLAT</v>
+      </c>
+      <c r="B16" t="str">
+        <v>פריט EXP-FLAT</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Test EXP-FLAT</v>
+      </c>
+      <c r="D16" t="str">
+        <v>ספק א</v>
+      </c>
+      <c r="E16" t="str">
+        <v>01</v>
+      </c>
+      <c r="F16" t="str">
+        <v>פעיל</v>
+      </c>
+      <c r="G16" t="str">
+        <v>ND</v>
+      </c>
+      <c r="H16" t="str">
+        <v>A</v>
+      </c>
+      <c r="I16">
+        <v>95</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>30</v>
+      </c>
+      <c r="M16">
+        <v>2</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>100</v>
+      </c>
+      <c r="P16" t="str">
+        <v>USD</v>
+      </c>
+      <c r="Q16">
+        <v>100</v>
+      </c>
+      <c r="R16">
+        <v>100</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>5</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16" t="str">
+        <v>Z004</v>
+      </c>
+      <c r="Y16" t="str">
+        <v>מנוע</v>
+      </c>
+      <c r="Z16" t="str">
+        <v>ZT</v>
+      </c>
+      <c r="AA16" t="str">
+        <v>מתכנן</v>
+      </c>
+      <c r="AB16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="str">
+        <v>שיווק</v>
+      </c>
+      <c r="AD16" t="str">
+        <v>מערכת</v>
+      </c>
+      <c r="AE16" t="str">
+        <v>100</v>
+      </c>
+      <c r="AF16" t="str">
+        <v>ZT</v>
+      </c>
+      <c r="AG16" t="str">
+        <v>200</v>
+      </c>
+      <c r="AH16" t="str">
+        <v>דגם</v>
+      </c>
+      <c r="AI16" t="str">
+        <v>300</v>
+      </c>
+      <c r="AJ16" t="str">
+        <v>מערכת</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="str">
+        <v>12.09.2026</v>
+      </c>
+      <c r="BA16" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:BA12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:BA16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tests/expedite-zmrp.xlsx
+++ b/tests/expedite-zmrp.xlsx
@@ -720,10 +720,10 @@
         <v>10</v>
       </c>
       <c r="AZ4" t="str">
-        <v>12.09.2026</v>
+        <v>13.09.2026</v>
       </c>
       <c r="BA4" t="str">
-        <v>24.07.2026</v>
+        <v>25.07.2026</v>
       </c>
     </row>
     <row r="5">
@@ -881,10 +881,10 @@
         <v>10</v>
       </c>
       <c r="AZ5" t="str">
-        <v>12.09.2026</v>
+        <v>13.09.2026</v>
       </c>
       <c r="BA5" t="str">
-        <v>24.07.2026</v>
+        <v>25.07.2026</v>
       </c>
     </row>
     <row r="6">
@@ -1042,10 +1042,10 @@
         <v>10</v>
       </c>
       <c r="AZ6" t="str">
-        <v>12.09.2026</v>
+        <v>13.09.2026</v>
       </c>
       <c r="BA6" t="str">
-        <v>24.07.2026</v>
+        <v>25.07.2026</v>
       </c>
     </row>
     <row r="7">
@@ -1203,10 +1203,10 @@
         <v>10</v>
       </c>
       <c r="AZ7" t="str">
-        <v>12.09.2026</v>
+        <v>13.09.2026</v>
       </c>
       <c r="BA7" t="str">
-        <v>24.07.2026</v>
+        <v>25.07.2026</v>
       </c>
     </row>
     <row r="8">
@@ -1364,10 +1364,10 @@
         <v>10</v>
       </c>
       <c r="AZ8" t="str">
-        <v>12.09.2026</v>
+        <v>13.09.2026</v>
       </c>
       <c r="BA8" t="str">
-        <v>24.07.2026</v>
+        <v>25.07.2026</v>
       </c>
     </row>
     <row r="9">
@@ -1525,10 +1525,10 @@
         <v>0</v>
       </c>
       <c r="AZ9" t="str">
-        <v>12.09.2026</v>
+        <v>13.09.2026</v>
       </c>
       <c r="BA9" t="str">
-        <v>24.07.2026</v>
+        <v>25.07.2026</v>
       </c>
     </row>
     <row r="10">
@@ -1686,10 +1686,10 @@
         <v>10</v>
       </c>
       <c r="AZ10" t="str">
-        <v>12.09.2026</v>
+        <v>13.09.2026</v>
       </c>
       <c r="BA10" t="str">
-        <v>24.07.2026</v>
+        <v>25.07.2026</v>
       </c>
     </row>
     <row r="11">
@@ -1847,10 +1847,10 @@
         <v>10</v>
       </c>
       <c r="AZ11" t="str">
-        <v>12.09.2026</v>
+        <v>13.09.2026</v>
       </c>
       <c r="BA11" t="str">
-        <v>24.07.2026</v>
+        <v>25.07.2026</v>
       </c>
     </row>
     <row r="12">
@@ -2008,10 +2008,10 @@
         <v>10</v>
       </c>
       <c r="AZ12" t="str">
-        <v>12.09.2026</v>
+        <v>13.09.2026</v>
       </c>
       <c r="BA12" t="str">
-        <v>24.07.2026</v>
+        <v>25.07.2026</v>
       </c>
     </row>
     <row r="13">
@@ -2169,10 +2169,10 @@
         <v>10</v>
       </c>
       <c r="AZ13" t="str">
-        <v>12.09.2026</v>
+        <v>13.09.2026</v>
       </c>
       <c r="BA13" t="str">
-        <v>05.04.2024</v>
+        <v>06.04.2024</v>
       </c>
     </row>
     <row r="14">
@@ -2330,10 +2330,10 @@
         <v>10</v>
       </c>
       <c r="AZ14" t="str">
-        <v>12.09.2026</v>
+        <v>13.09.2026</v>
       </c>
       <c r="BA14" t="str">
-        <v>06.03.2026</v>
+        <v>07.03.2026</v>
       </c>
     </row>
     <row r="15">
@@ -2491,7 +2491,7 @@
         <v>10</v>
       </c>
       <c r="AZ15" t="str">
-        <v>12.09.2026</v>
+        <v>13.09.2026</v>
       </c>
       <c r="BA15" t="str">
         <v/>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="AZ16" t="str">
-        <v>12.09.2026</v>
+        <v>13.09.2026</v>
       </c>
       <c r="BA16" t="str">
         <v/>

--- a/tests/expedite-zmrp.xlsx
+++ b/tests/expedite-zmrp.xlsx
@@ -720,10 +720,10 @@
         <v>10</v>
       </c>
       <c r="AZ4" t="str">
-        <v>13.09.2026</v>
+        <v>14.09.2026</v>
       </c>
       <c r="BA4" t="str">
-        <v>25.07.2026</v>
+        <v>26.07.2026</v>
       </c>
     </row>
     <row r="5">
@@ -881,10 +881,10 @@
         <v>10</v>
       </c>
       <c r="AZ5" t="str">
-        <v>13.09.2026</v>
+        <v>14.09.2026</v>
       </c>
       <c r="BA5" t="str">
-        <v>25.07.2026</v>
+        <v>26.07.2026</v>
       </c>
     </row>
     <row r="6">
@@ -1042,10 +1042,10 @@
         <v>10</v>
       </c>
       <c r="AZ6" t="str">
-        <v>13.09.2026</v>
+        <v>14.09.2026</v>
       </c>
       <c r="BA6" t="str">
-        <v>25.07.2026</v>
+        <v>26.07.2026</v>
       </c>
     </row>
     <row r="7">
@@ -1203,10 +1203,10 @@
         <v>10</v>
       </c>
       <c r="AZ7" t="str">
-        <v>13.09.2026</v>
+        <v>14.09.2026</v>
       </c>
       <c r="BA7" t="str">
-        <v>25.07.2026</v>
+        <v>26.07.2026</v>
       </c>
     </row>
     <row r="8">
@@ -1364,10 +1364,10 @@
         <v>10</v>
       </c>
       <c r="AZ8" t="str">
-        <v>13.09.2026</v>
+        <v>14.09.2026</v>
       </c>
       <c r="BA8" t="str">
-        <v>25.07.2026</v>
+        <v>26.07.2026</v>
       </c>
     </row>
     <row r="9">
@@ -1525,10 +1525,10 @@
         <v>0</v>
       </c>
       <c r="AZ9" t="str">
-        <v>13.09.2026</v>
+        <v>14.09.2026</v>
       </c>
       <c r="BA9" t="str">
-        <v>25.07.2026</v>
+        <v>26.07.2026</v>
       </c>
     </row>
     <row r="10">
@@ -1686,10 +1686,10 @@
         <v>10</v>
       </c>
       <c r="AZ10" t="str">
-        <v>13.09.2026</v>
+        <v>14.09.2026</v>
       </c>
       <c r="BA10" t="str">
-        <v>25.07.2026</v>
+        <v>26.07.2026</v>
       </c>
     </row>
     <row r="11">
@@ -1847,10 +1847,10 @@
         <v>10</v>
       </c>
       <c r="AZ11" t="str">
-        <v>13.09.2026</v>
+        <v>14.09.2026</v>
       </c>
       <c r="BA11" t="str">
-        <v>25.07.2026</v>
+        <v>26.07.2026</v>
       </c>
     </row>
     <row r="12">
@@ -2008,10 +2008,10 @@
         <v>10</v>
       </c>
       <c r="AZ12" t="str">
-        <v>13.09.2026</v>
+        <v>14.09.2026</v>
       </c>
       <c r="BA12" t="str">
-        <v>25.07.2026</v>
+        <v>26.07.2026</v>
       </c>
     </row>
     <row r="13">
@@ -2169,10 +2169,10 @@
         <v>10</v>
       </c>
       <c r="AZ13" t="str">
-        <v>13.09.2026</v>
+        <v>14.09.2026</v>
       </c>
       <c r="BA13" t="str">
-        <v>06.04.2024</v>
+        <v>07.04.2024</v>
       </c>
     </row>
     <row r="14">
@@ -2330,10 +2330,10 @@
         <v>10</v>
       </c>
       <c r="AZ14" t="str">
-        <v>13.09.2026</v>
+        <v>14.09.2026</v>
       </c>
       <c r="BA14" t="str">
-        <v>07.03.2026</v>
+        <v>08.03.2026</v>
       </c>
     </row>
     <row r="15">
@@ -2491,7 +2491,7 @@
         <v>10</v>
       </c>
       <c r="AZ15" t="str">
-        <v>13.09.2026</v>
+        <v>14.09.2026</v>
       </c>
       <c r="BA15" t="str">
         <v/>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="AZ16" t="str">
-        <v>13.09.2026</v>
+        <v>14.09.2026</v>
       </c>
       <c r="BA16" t="str">
         <v/>

--- a/tests/expedite-zmrp.xlsx
+++ b/tests/expedite-zmrp.xlsx
@@ -720,10 +720,10 @@
         <v>10</v>
       </c>
       <c r="AZ4" t="str">
-        <v>14.09.2026</v>
+        <v>16.09.2026</v>
       </c>
       <c r="BA4" t="str">
-        <v>26.07.2026</v>
+        <v>28.07.2026</v>
       </c>
     </row>
     <row r="5">
@@ -881,10 +881,10 @@
         <v>10</v>
       </c>
       <c r="AZ5" t="str">
-        <v>14.09.2026</v>
+        <v>16.09.2026</v>
       </c>
       <c r="BA5" t="str">
-        <v>26.07.2026</v>
+        <v>28.07.2026</v>
       </c>
     </row>
     <row r="6">
@@ -1042,10 +1042,10 @@
         <v>10</v>
       </c>
       <c r="AZ6" t="str">
-        <v>14.09.2026</v>
+        <v>16.09.2026</v>
       </c>
       <c r="BA6" t="str">
-        <v>26.07.2026</v>
+        <v>28.07.2026</v>
       </c>
     </row>
     <row r="7">
@@ -1203,10 +1203,10 @@
         <v>10</v>
       </c>
       <c r="AZ7" t="str">
-        <v>14.09.2026</v>
+        <v>16.09.2026</v>
       </c>
       <c r="BA7" t="str">
-        <v>26.07.2026</v>
+        <v>28.07.2026</v>
       </c>
     </row>
     <row r="8">
@@ -1364,10 +1364,10 @@
         <v>10</v>
       </c>
       <c r="AZ8" t="str">
-        <v>14.09.2026</v>
+        <v>16.09.2026</v>
       </c>
       <c r="BA8" t="str">
-        <v>26.07.2026</v>
+        <v>28.07.2026</v>
       </c>
     </row>
     <row r="9">
@@ -1525,10 +1525,10 @@
         <v>0</v>
       </c>
       <c r="AZ9" t="str">
-        <v>14.09.2026</v>
+        <v>16.09.2026</v>
       </c>
       <c r="BA9" t="str">
-        <v>26.07.2026</v>
+        <v>28.07.2026</v>
       </c>
     </row>
     <row r="10">
@@ -1686,10 +1686,10 @@
         <v>10</v>
       </c>
       <c r="AZ10" t="str">
-        <v>14.09.2026</v>
+        <v>16.09.2026</v>
       </c>
       <c r="BA10" t="str">
-        <v>26.07.2026</v>
+        <v>28.07.2026</v>
       </c>
     </row>
     <row r="11">
@@ -1847,10 +1847,10 @@
         <v>10</v>
       </c>
       <c r="AZ11" t="str">
-        <v>14.09.2026</v>
+        <v>16.09.2026</v>
       </c>
       <c r="BA11" t="str">
-        <v>26.07.2026</v>
+        <v>28.07.2026</v>
       </c>
     </row>
     <row r="12">
@@ -2008,10 +2008,10 @@
         <v>10</v>
       </c>
       <c r="AZ12" t="str">
-        <v>14.09.2026</v>
+        <v>16.09.2026</v>
       </c>
       <c r="BA12" t="str">
-        <v>26.07.2026</v>
+        <v>28.07.2026</v>
       </c>
     </row>
     <row r="13">
@@ -2169,10 +2169,10 @@
         <v>10</v>
       </c>
       <c r="AZ13" t="str">
-        <v>14.09.2026</v>
+        <v>16.09.2026</v>
       </c>
       <c r="BA13" t="str">
-        <v>07.04.2024</v>
+        <v>09.04.2024</v>
       </c>
     </row>
     <row r="14">
@@ -2330,10 +2330,10 @@
         <v>10</v>
       </c>
       <c r="AZ14" t="str">
-        <v>14.09.2026</v>
+        <v>16.09.2026</v>
       </c>
       <c r="BA14" t="str">
-        <v>08.03.2026</v>
+        <v>10.03.2026</v>
       </c>
     </row>
     <row r="15">
@@ -2491,7 +2491,7 @@
         <v>10</v>
       </c>
       <c r="AZ15" t="str">
-        <v>14.09.2026</v>
+        <v>16.09.2026</v>
       </c>
       <c r="BA15" t="str">
         <v/>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="AZ16" t="str">
-        <v>14.09.2026</v>
+        <v>16.09.2026</v>
       </c>
       <c r="BA16" t="str">
         <v/>

--- a/tests/expedite-zmrp.xlsx
+++ b/tests/expedite-zmrp.xlsx
@@ -720,10 +720,10 @@
         <v>10</v>
       </c>
       <c r="AZ4" t="str">
-        <v>16.09.2026</v>
+        <v>17.09.2026</v>
       </c>
       <c r="BA4" t="str">
-        <v>28.07.2026</v>
+        <v>29.07.2026</v>
       </c>
     </row>
     <row r="5">
@@ -881,10 +881,10 @@
         <v>10</v>
       </c>
       <c r="AZ5" t="str">
-        <v>16.09.2026</v>
+        <v>17.09.2026</v>
       </c>
       <c r="BA5" t="str">
-        <v>28.07.2026</v>
+        <v>29.07.2026</v>
       </c>
     </row>
     <row r="6">
@@ -1042,10 +1042,10 @@
         <v>10</v>
       </c>
       <c r="AZ6" t="str">
-        <v>16.09.2026</v>
+        <v>17.09.2026</v>
       </c>
       <c r="BA6" t="str">
-        <v>28.07.2026</v>
+        <v>29.07.2026</v>
       </c>
     </row>
     <row r="7">
@@ -1203,10 +1203,10 @@
         <v>10</v>
       </c>
       <c r="AZ7" t="str">
-        <v>16.09.2026</v>
+        <v>17.09.2026</v>
       </c>
       <c r="BA7" t="str">
-        <v>28.07.2026</v>
+        <v>29.07.2026</v>
       </c>
     </row>
     <row r="8">
@@ -1364,10 +1364,10 @@
         <v>10</v>
       </c>
       <c r="AZ8" t="str">
-        <v>16.09.2026</v>
+        <v>17.09.2026</v>
       </c>
       <c r="BA8" t="str">
-        <v>28.07.2026</v>
+        <v>29.07.2026</v>
       </c>
     </row>
     <row r="9">
@@ -1525,10 +1525,10 @@
         <v>0</v>
       </c>
       <c r="AZ9" t="str">
-        <v>16.09.2026</v>
+        <v>17.09.2026</v>
       </c>
       <c r="BA9" t="str">
-        <v>28.07.2026</v>
+        <v>29.07.2026</v>
       </c>
     </row>
     <row r="10">
@@ -1686,10 +1686,10 @@
         <v>10</v>
       </c>
       <c r="AZ10" t="str">
-        <v>16.09.2026</v>
+        <v>17.09.2026</v>
       </c>
       <c r="BA10" t="str">
-        <v>28.07.2026</v>
+        <v>29.07.2026</v>
       </c>
     </row>
     <row r="11">
@@ -1847,10 +1847,10 @@
         <v>10</v>
       </c>
       <c r="AZ11" t="str">
-        <v>16.09.2026</v>
+        <v>17.09.2026</v>
       </c>
       <c r="BA11" t="str">
-        <v>28.07.2026</v>
+        <v>29.07.2026</v>
       </c>
     </row>
     <row r="12">
@@ -2008,10 +2008,10 @@
         <v>10</v>
       </c>
       <c r="AZ12" t="str">
-        <v>16.09.2026</v>
+        <v>17.09.2026</v>
       </c>
       <c r="BA12" t="str">
-        <v>28.07.2026</v>
+        <v>29.07.2026</v>
       </c>
     </row>
     <row r="13">
@@ -2169,10 +2169,10 @@
         <v>10</v>
       </c>
       <c r="AZ13" t="str">
-        <v>16.09.2026</v>
+        <v>17.09.2026</v>
       </c>
       <c r="BA13" t="str">
-        <v>09.04.2024</v>
+        <v>10.04.2024</v>
       </c>
     </row>
     <row r="14">
@@ -2330,10 +2330,10 @@
         <v>10</v>
       </c>
       <c r="AZ14" t="str">
-        <v>16.09.2026</v>
+        <v>17.09.2026</v>
       </c>
       <c r="BA14" t="str">
-        <v>10.03.2026</v>
+        <v>11.03.2026</v>
       </c>
     </row>
     <row r="15">
@@ -2491,7 +2491,7 @@
         <v>10</v>
       </c>
       <c r="AZ15" t="str">
-        <v>16.09.2026</v>
+        <v>17.09.2026</v>
       </c>
       <c r="BA15" t="str">
         <v/>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="AZ16" t="str">
-        <v>16.09.2026</v>
+        <v>17.09.2026</v>
       </c>
       <c r="BA16" t="str">
         <v/>

--- a/tests/expedite-zmrp.xlsx
+++ b/tests/expedite-zmrp.xlsx
@@ -720,10 +720,10 @@
         <v>10</v>
       </c>
       <c r="AZ4" t="str">
-        <v>17.09.2026</v>
+        <v>19.09.2026</v>
       </c>
       <c r="BA4" t="str">
-        <v>29.07.2026</v>
+        <v>31.07.2026</v>
       </c>
     </row>
     <row r="5">
@@ -881,10 +881,10 @@
         <v>10</v>
       </c>
       <c r="AZ5" t="str">
-        <v>17.09.2026</v>
+        <v>19.09.2026</v>
       </c>
       <c r="BA5" t="str">
-        <v>29.07.2026</v>
+        <v>31.07.2026</v>
       </c>
     </row>
     <row r="6">
@@ -1042,10 +1042,10 @@
         <v>10</v>
       </c>
       <c r="AZ6" t="str">
-        <v>17.09.2026</v>
+        <v>19.09.2026</v>
       </c>
       <c r="BA6" t="str">
-        <v>29.07.2026</v>
+        <v>31.07.2026</v>
       </c>
     </row>
     <row r="7">
@@ -1203,10 +1203,10 @@
         <v>10</v>
       </c>
       <c r="AZ7" t="str">
-        <v>17.09.2026</v>
+        <v>19.09.2026</v>
       </c>
       <c r="BA7" t="str">
-        <v>29.07.2026</v>
+        <v>31.07.2026</v>
       </c>
     </row>
     <row r="8">
@@ -1364,10 +1364,10 @@
         <v>10</v>
       </c>
       <c r="AZ8" t="str">
-        <v>17.09.2026</v>
+        <v>19.09.2026</v>
       </c>
       <c r="BA8" t="str">
-        <v>29.07.2026</v>
+        <v>31.07.2026</v>
       </c>
     </row>
     <row r="9">
@@ -1525,10 +1525,10 @@
         <v>0</v>
       </c>
       <c r="AZ9" t="str">
-        <v>17.09.2026</v>
+        <v>19.09.2026</v>
       </c>
       <c r="BA9" t="str">
-        <v>29.07.2026</v>
+        <v>31.07.2026</v>
       </c>
     </row>
     <row r="10">
@@ -1686,10 +1686,10 @@
         <v>10</v>
       </c>
       <c r="AZ10" t="str">
-        <v>17.09.2026</v>
+        <v>19.09.2026</v>
       </c>
       <c r="BA10" t="str">
-        <v>29.07.2026</v>
+        <v>31.07.2026</v>
       </c>
     </row>
     <row r="11">
@@ -1847,10 +1847,10 @@
         <v>10</v>
       </c>
       <c r="AZ11" t="str">
-        <v>17.09.2026</v>
+        <v>19.09.2026</v>
       </c>
       <c r="BA11" t="str">
-        <v>29.07.2026</v>
+        <v>31.07.2026</v>
       </c>
     </row>
     <row r="12">
@@ -2008,10 +2008,10 @@
         <v>10</v>
       </c>
       <c r="AZ12" t="str">
-        <v>17.09.2026</v>
+        <v>19.09.2026</v>
       </c>
       <c r="BA12" t="str">
-        <v>29.07.2026</v>
+        <v>31.07.2026</v>
       </c>
     </row>
     <row r="13">
@@ -2169,10 +2169,10 @@
         <v>10</v>
       </c>
       <c r="AZ13" t="str">
-        <v>17.09.2026</v>
+        <v>19.09.2026</v>
       </c>
       <c r="BA13" t="str">
-        <v>10.04.2024</v>
+        <v>12.04.2024</v>
       </c>
     </row>
     <row r="14">
@@ -2330,10 +2330,10 @@
         <v>10</v>
       </c>
       <c r="AZ14" t="str">
-        <v>17.09.2026</v>
+        <v>19.09.2026</v>
       </c>
       <c r="BA14" t="str">
-        <v>11.03.2026</v>
+        <v>13.03.2026</v>
       </c>
     </row>
     <row r="15">
@@ -2491,7 +2491,7 @@
         <v>10</v>
       </c>
       <c r="AZ15" t="str">
-        <v>17.09.2026</v>
+        <v>19.09.2026</v>
       </c>
       <c r="BA15" t="str">
         <v/>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="AZ16" t="str">
-        <v>17.09.2026</v>
+        <v>19.09.2026</v>
       </c>
       <c r="BA16" t="str">
         <v/>

--- a/tests/expedite-zmrp.xlsx
+++ b/tests/expedite-zmrp.xlsx
@@ -720,10 +720,10 @@
         <v>10</v>
       </c>
       <c r="AZ4" t="str">
-        <v>19.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA4" t="str">
-        <v>31.07.2026</v>
+        <v>01.08.2026</v>
       </c>
     </row>
     <row r="5">
@@ -881,10 +881,10 @@
         <v>10</v>
       </c>
       <c r="AZ5" t="str">
-        <v>19.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA5" t="str">
-        <v>31.07.2026</v>
+        <v>01.08.2026</v>
       </c>
     </row>
     <row r="6">
@@ -1042,10 +1042,10 @@
         <v>10</v>
       </c>
       <c r="AZ6" t="str">
-        <v>19.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA6" t="str">
-        <v>31.07.2026</v>
+        <v>01.08.2026</v>
       </c>
     </row>
     <row r="7">
@@ -1203,10 +1203,10 @@
         <v>10</v>
       </c>
       <c r="AZ7" t="str">
-        <v>19.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA7" t="str">
-        <v>31.07.2026</v>
+        <v>01.08.2026</v>
       </c>
     </row>
     <row r="8">
@@ -1364,10 +1364,10 @@
         <v>10</v>
       </c>
       <c r="AZ8" t="str">
-        <v>19.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA8" t="str">
-        <v>31.07.2026</v>
+        <v>01.08.2026</v>
       </c>
     </row>
     <row r="9">
@@ -1525,10 +1525,10 @@
         <v>0</v>
       </c>
       <c r="AZ9" t="str">
-        <v>19.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA9" t="str">
-        <v>31.07.2026</v>
+        <v>01.08.2026</v>
       </c>
     </row>
     <row r="10">
@@ -1686,10 +1686,10 @@
         <v>10</v>
       </c>
       <c r="AZ10" t="str">
-        <v>19.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA10" t="str">
-        <v>31.07.2026</v>
+        <v>01.08.2026</v>
       </c>
     </row>
     <row r="11">
@@ -1847,10 +1847,10 @@
         <v>10</v>
       </c>
       <c r="AZ11" t="str">
-        <v>19.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA11" t="str">
-        <v>31.07.2026</v>
+        <v>01.08.2026</v>
       </c>
     </row>
     <row r="12">
@@ -2008,10 +2008,10 @@
         <v>10</v>
       </c>
       <c r="AZ12" t="str">
-        <v>19.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA12" t="str">
-        <v>31.07.2026</v>
+        <v>01.08.2026</v>
       </c>
     </row>
     <row r="13">
@@ -2169,10 +2169,10 @@
         <v>10</v>
       </c>
       <c r="AZ13" t="str">
-        <v>19.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA13" t="str">
-        <v>12.04.2024</v>
+        <v>13.04.2024</v>
       </c>
     </row>
     <row r="14">
@@ -2330,10 +2330,10 @@
         <v>10</v>
       </c>
       <c r="AZ14" t="str">
-        <v>19.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA14" t="str">
-        <v>13.03.2026</v>
+        <v>14.03.2026</v>
       </c>
     </row>
     <row r="15">
@@ -2491,7 +2491,7 @@
         <v>10</v>
       </c>
       <c r="AZ15" t="str">
-        <v>19.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA15" t="str">
         <v/>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="AZ16" t="str">
-        <v>19.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA16" t="str">
         <v/>

--- a/tests/expedite-zmrp.xlsx
+++ b/tests/expedite-zmrp.xlsx
@@ -720,10 +720,10 @@
         <v>10</v>
       </c>
       <c r="AZ4" t="str">
-        <v>17.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA4" t="str">
-        <v>29.07.2026</v>
+        <v>01.08.2026</v>
       </c>
     </row>
     <row r="5">
@@ -881,10 +881,10 @@
         <v>10</v>
       </c>
       <c r="AZ5" t="str">
-        <v>17.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA5" t="str">
-        <v>29.07.2026</v>
+        <v>01.08.2026</v>
       </c>
     </row>
     <row r="6">
@@ -1042,10 +1042,10 @@
         <v>10</v>
       </c>
       <c r="AZ6" t="str">
-        <v>17.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA6" t="str">
-        <v>29.07.2026</v>
+        <v>01.08.2026</v>
       </c>
     </row>
     <row r="7">
@@ -1203,10 +1203,10 @@
         <v>10</v>
       </c>
       <c r="AZ7" t="str">
-        <v>17.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA7" t="str">
-        <v>29.07.2026</v>
+        <v>01.08.2026</v>
       </c>
     </row>
     <row r="8">
@@ -1364,10 +1364,10 @@
         <v>10</v>
       </c>
       <c r="AZ8" t="str">
-        <v>17.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA8" t="str">
-        <v>29.07.2026</v>
+        <v>01.08.2026</v>
       </c>
     </row>
     <row r="9">
@@ -1525,10 +1525,10 @@
         <v>0</v>
       </c>
       <c r="AZ9" t="str">
-        <v>17.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA9" t="str">
-        <v>29.07.2026</v>
+        <v>01.08.2026</v>
       </c>
     </row>
     <row r="10">
@@ -1686,10 +1686,10 @@
         <v>10</v>
       </c>
       <c r="AZ10" t="str">
-        <v>17.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA10" t="str">
-        <v>29.07.2026</v>
+        <v>01.08.2026</v>
       </c>
     </row>
     <row r="11">
@@ -1847,10 +1847,10 @@
         <v>10</v>
       </c>
       <c r="AZ11" t="str">
-        <v>17.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA11" t="str">
-        <v>29.07.2026</v>
+        <v>01.08.2026</v>
       </c>
     </row>
     <row r="12">
@@ -2008,10 +2008,10 @@
         <v>10</v>
       </c>
       <c r="AZ12" t="str">
-        <v>17.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA12" t="str">
-        <v>29.07.2026</v>
+        <v>01.08.2026</v>
       </c>
     </row>
     <row r="13">
@@ -2169,10 +2169,10 @@
         <v>10</v>
       </c>
       <c r="AZ13" t="str">
-        <v>17.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA13" t="str">
-        <v>10.04.2024</v>
+        <v>13.04.2024</v>
       </c>
     </row>
     <row r="14">
@@ -2330,10 +2330,10 @@
         <v>10</v>
       </c>
       <c r="AZ14" t="str">
-        <v>17.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA14" t="str">
-        <v>11.03.2026</v>
+        <v>14.03.2026</v>
       </c>
     </row>
     <row r="15">
@@ -2491,7 +2491,7 @@
         <v>10</v>
       </c>
       <c r="AZ15" t="str">
-        <v>17.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA15" t="str">
         <v/>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="AZ16" t="str">
-        <v>17.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BA16" t="str">
         <v/>

--- a/tests/expedite-zmrp.xlsx
+++ b/tests/expedite-zmrp.xlsx
@@ -720,10 +720,10 @@
         <v>10</v>
       </c>
       <c r="AZ4" t="str">
-        <v>20.09.2026</v>
+        <v>24.09.2026</v>
       </c>
       <c r="BA4" t="str">
-        <v>01.08.2026</v>
+        <v>05.08.2026</v>
       </c>
     </row>
     <row r="5">
@@ -881,10 +881,10 @@
         <v>10</v>
       </c>
       <c r="AZ5" t="str">
-        <v>20.09.2026</v>
+        <v>24.09.2026</v>
       </c>
       <c r="BA5" t="str">
-        <v>01.08.2026</v>
+        <v>05.08.2026</v>
       </c>
     </row>
     <row r="6">
@@ -1042,10 +1042,10 @@
         <v>10</v>
       </c>
       <c r="AZ6" t="str">
-        <v>20.09.2026</v>
+        <v>24.09.2026</v>
       </c>
       <c r="BA6" t="str">
-        <v>01.08.2026</v>
+        <v>05.08.2026</v>
       </c>
     </row>
     <row r="7">
@@ -1203,10 +1203,10 @@
         <v>10</v>
       </c>
       <c r="AZ7" t="str">
-        <v>20.09.2026</v>
+        <v>24.09.2026</v>
       </c>
       <c r="BA7" t="str">
-        <v>01.08.2026</v>
+        <v>05.08.2026</v>
       </c>
     </row>
     <row r="8">
@@ -1364,10 +1364,10 @@
         <v>10</v>
       </c>
       <c r="AZ8" t="str">
-        <v>20.09.2026</v>
+        <v>24.09.2026</v>
       </c>
       <c r="BA8" t="str">
-        <v>01.08.2026</v>
+        <v>05.08.2026</v>
       </c>
     </row>
     <row r="9">
@@ -1525,10 +1525,10 @@
         <v>0</v>
       </c>
       <c r="AZ9" t="str">
-        <v>20.09.2026</v>
+        <v>24.09.2026</v>
       </c>
       <c r="BA9" t="str">
-        <v>01.08.2026</v>
+        <v>05.08.2026</v>
       </c>
     </row>
     <row r="10">
@@ -1686,10 +1686,10 @@
         <v>10</v>
       </c>
       <c r="AZ10" t="str">
-        <v>20.09.2026</v>
+        <v>24.09.2026</v>
       </c>
       <c r="BA10" t="str">
-        <v>01.08.2026</v>
+        <v>05.08.2026</v>
       </c>
     </row>
     <row r="11">
@@ -1847,10 +1847,10 @@
         <v>10</v>
       </c>
       <c r="AZ11" t="str">
-        <v>20.09.2026</v>
+        <v>24.09.2026</v>
       </c>
       <c r="BA11" t="str">
-        <v>01.08.2026</v>
+        <v>05.08.2026</v>
       </c>
     </row>
     <row r="12">
@@ -2008,10 +2008,10 @@
         <v>10</v>
       </c>
       <c r="AZ12" t="str">
-        <v>20.09.2026</v>
+        <v>24.09.2026</v>
       </c>
       <c r="BA12" t="str">
-        <v>01.08.2026</v>
+        <v>05.08.2026</v>
       </c>
     </row>
     <row r="13">
@@ -2169,10 +2169,10 @@
         <v>10</v>
       </c>
       <c r="AZ13" t="str">
-        <v>20.09.2026</v>
+        <v>24.09.2026</v>
       </c>
       <c r="BA13" t="str">
-        <v>13.04.2024</v>
+        <v>17.04.2024</v>
       </c>
     </row>
     <row r="14">
@@ -2330,10 +2330,10 @@
         <v>10</v>
       </c>
       <c r="AZ14" t="str">
-        <v>20.09.2026</v>
+        <v>24.09.2026</v>
       </c>
       <c r="BA14" t="str">
-        <v>14.03.2026</v>
+        <v>18.03.2026</v>
       </c>
     </row>
     <row r="15">
@@ -2491,7 +2491,7 @@
         <v>10</v>
       </c>
       <c r="AZ15" t="str">
-        <v>20.09.2026</v>
+        <v>24.09.2026</v>
       </c>
       <c r="BA15" t="str">
         <v/>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="AZ16" t="str">
-        <v>20.09.2026</v>
+        <v>24.09.2026</v>
       </c>
       <c r="BA16" t="str">
         <v/>

--- a/tests/expedite-zmrp.xlsx
+++ b/tests/expedite-zmrp.xlsx
@@ -720,10 +720,10 @@
         <v>10</v>
       </c>
       <c r="AZ4" t="str">
-        <v>24.09.2026</v>
+        <v>25.09.2026</v>
       </c>
       <c r="BA4" t="str">
-        <v>05.08.2026</v>
+        <v>06.08.2026</v>
       </c>
     </row>
     <row r="5">
@@ -881,10 +881,10 @@
         <v>10</v>
       </c>
       <c r="AZ5" t="str">
-        <v>24.09.2026</v>
+        <v>25.09.2026</v>
       </c>
       <c r="BA5" t="str">
-        <v>05.08.2026</v>
+        <v>06.08.2026</v>
       </c>
     </row>
     <row r="6">
@@ -1042,10 +1042,10 @@
         <v>10</v>
       </c>
       <c r="AZ6" t="str">
-        <v>24.09.2026</v>
+        <v>25.09.2026</v>
       </c>
       <c r="BA6" t="str">
-        <v>05.08.2026</v>
+        <v>06.08.2026</v>
       </c>
     </row>
     <row r="7">
@@ -1203,10 +1203,10 @@
         <v>10</v>
       </c>
       <c r="AZ7" t="str">
-        <v>24.09.2026</v>
+        <v>25.09.2026</v>
       </c>
       <c r="BA7" t="str">
-        <v>05.08.2026</v>
+        <v>06.08.2026</v>
       </c>
     </row>
     <row r="8">
@@ -1364,10 +1364,10 @@
         <v>10</v>
       </c>
       <c r="AZ8" t="str">
-        <v>24.09.2026</v>
+        <v>25.09.2026</v>
       </c>
       <c r="BA8" t="str">
-        <v>05.08.2026</v>
+        <v>06.08.2026</v>
       </c>
     </row>
     <row r="9">
@@ -1525,10 +1525,10 @@
         <v>0</v>
       </c>
       <c r="AZ9" t="str">
-        <v>24.09.2026</v>
+        <v>25.09.2026</v>
       </c>
       <c r="BA9" t="str">
-        <v>05.08.2026</v>
+        <v>06.08.2026</v>
       </c>
     </row>
     <row r="10">
@@ -1686,10 +1686,10 @@
         <v>10</v>
       </c>
       <c r="AZ10" t="str">
-        <v>24.09.2026</v>
+        <v>25.09.2026</v>
       </c>
       <c r="BA10" t="str">
-        <v>05.08.2026</v>
+        <v>06.08.2026</v>
       </c>
     </row>
     <row r="11">
@@ -1847,10 +1847,10 @@
         <v>10</v>
       </c>
       <c r="AZ11" t="str">
-        <v>24.09.2026</v>
+        <v>25.09.2026</v>
       </c>
       <c r="BA11" t="str">
-        <v>05.08.2026</v>
+        <v>06.08.2026</v>
       </c>
     </row>
     <row r="12">
@@ -2008,10 +2008,10 @@
         <v>10</v>
       </c>
       <c r="AZ12" t="str">
-        <v>24.09.2026</v>
+        <v>25.09.2026</v>
       </c>
       <c r="BA12" t="str">
-        <v>05.08.2026</v>
+        <v>06.08.2026</v>
       </c>
     </row>
     <row r="13">
@@ -2169,10 +2169,10 @@
         <v>10</v>
       </c>
       <c r="AZ13" t="str">
-        <v>24.09.2026</v>
+        <v>25.09.2026</v>
       </c>
       <c r="BA13" t="str">
-        <v>17.04.2024</v>
+        <v>18.04.2024</v>
       </c>
     </row>
     <row r="14">
@@ -2330,10 +2330,10 @@
         <v>10</v>
       </c>
       <c r="AZ14" t="str">
-        <v>24.09.2026</v>
+        <v>25.09.2026</v>
       </c>
       <c r="BA14" t="str">
-        <v>18.03.2026</v>
+        <v>19.03.2026</v>
       </c>
     </row>
     <row r="15">
@@ -2491,7 +2491,7 @@
         <v>10</v>
       </c>
       <c r="AZ15" t="str">
-        <v>24.09.2026</v>
+        <v>25.09.2026</v>
       </c>
       <c r="BA15" t="str">
         <v/>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="AZ16" t="str">
-        <v>24.09.2026</v>
+        <v>25.09.2026</v>
       </c>
       <c r="BA16" t="str">
         <v/>

--- a/tests/expedite-zmrp.xlsx
+++ b/tests/expedite-zmrp.xlsx
@@ -720,10 +720,10 @@
         <v>10</v>
       </c>
       <c r="AZ4" t="str">
-        <v>25.09.2026</v>
+        <v>26.09.2026</v>
       </c>
       <c r="BA4" t="str">
-        <v>06.08.2026</v>
+        <v>07.08.2026</v>
       </c>
     </row>
     <row r="5">
@@ -881,10 +881,10 @@
         <v>10</v>
       </c>
       <c r="AZ5" t="str">
-        <v>25.09.2026</v>
+        <v>26.09.2026</v>
       </c>
       <c r="BA5" t="str">
-        <v>06.08.2026</v>
+        <v>07.08.2026</v>
       </c>
     </row>
     <row r="6">
@@ -1042,10 +1042,10 @@
         <v>10</v>
       </c>
       <c r="AZ6" t="str">
-        <v>25.09.2026</v>
+        <v>26.09.2026</v>
       </c>
       <c r="BA6" t="str">
-        <v>06.08.2026</v>
+        <v>07.08.2026</v>
       </c>
     </row>
     <row r="7">
@@ -1203,10 +1203,10 @@
         <v>10</v>
       </c>
       <c r="AZ7" t="str">
-        <v>25.09.2026</v>
+        <v>26.09.2026</v>
       </c>
       <c r="BA7" t="str">
-        <v>06.08.2026</v>
+        <v>07.08.2026</v>
       </c>
     </row>
     <row r="8">
@@ -1364,10 +1364,10 @@
         <v>10</v>
       </c>
       <c r="AZ8" t="str">
-        <v>25.09.2026</v>
+        <v>26.09.2026</v>
       </c>
       <c r="BA8" t="str">
-        <v>06.08.2026</v>
+        <v>07.08.2026</v>
       </c>
     </row>
     <row r="9">
@@ -1525,10 +1525,10 @@
         <v>0</v>
       </c>
       <c r="AZ9" t="str">
-        <v>25.09.2026</v>
+        <v>26.09.2026</v>
       </c>
       <c r="BA9" t="str">
-        <v>06.08.2026</v>
+        <v>07.08.2026</v>
       </c>
     </row>
     <row r="10">
@@ -1686,10 +1686,10 @@
         <v>10</v>
       </c>
       <c r="AZ10" t="str">
-        <v>25.09.2026</v>
+        <v>26.09.2026</v>
       </c>
       <c r="BA10" t="str">
-        <v>06.08.2026</v>
+        <v>07.08.2026</v>
       </c>
     </row>
     <row r="11">
@@ -1847,10 +1847,10 @@
         <v>10</v>
       </c>
       <c r="AZ11" t="str">
-        <v>25.09.2026</v>
+        <v>26.09.2026</v>
       </c>
       <c r="BA11" t="str">
-        <v>06.08.2026</v>
+        <v>07.08.2026</v>
       </c>
     </row>
     <row r="12">
@@ -2008,10 +2008,10 @@
         <v>10</v>
       </c>
       <c r="AZ12" t="str">
-        <v>25.09.2026</v>
+        <v>26.09.2026</v>
       </c>
       <c r="BA12" t="str">
-        <v>06.08.2026</v>
+        <v>07.08.2026</v>
       </c>
     </row>
     <row r="13">
@@ -2169,10 +2169,10 @@
         <v>10</v>
       </c>
       <c r="AZ13" t="str">
-        <v>25.09.2026</v>
+        <v>26.09.2026</v>
       </c>
       <c r="BA13" t="str">
-        <v>18.04.2024</v>
+        <v>19.04.2024</v>
       </c>
     </row>
     <row r="14">
@@ -2330,10 +2330,10 @@
         <v>10</v>
       </c>
       <c r="AZ14" t="str">
-        <v>25.09.2026</v>
+        <v>26.09.2026</v>
       </c>
       <c r="BA14" t="str">
-        <v>19.03.2026</v>
+        <v>20.03.2026</v>
       </c>
     </row>
     <row r="15">
@@ -2491,7 +2491,7 @@
         <v>10</v>
       </c>
       <c r="AZ15" t="str">
-        <v>25.09.2026</v>
+        <v>26.09.2026</v>
       </c>
       <c r="BA15" t="str">
         <v/>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="AZ16" t="str">
-        <v>25.09.2026</v>
+        <v>26.09.2026</v>
       </c>
       <c r="BA16" t="str">
         <v/>

--- a/tests/expedite-zmrp.xlsx
+++ b/tests/expedite-zmrp.xlsx
@@ -720,10 +720,10 @@
         <v>10</v>
       </c>
       <c r="AZ4" t="str">
-        <v>26.09.2026</v>
+        <v>27.09.2026</v>
       </c>
       <c r="BA4" t="str">
-        <v>07.08.2026</v>
+        <v>08.08.2026</v>
       </c>
     </row>
     <row r="5">
@@ -881,10 +881,10 @@
         <v>10</v>
       </c>
       <c r="AZ5" t="str">
-        <v>26.09.2026</v>
+        <v>27.09.2026</v>
       </c>
       <c r="BA5" t="str">
-        <v>07.08.2026</v>
+        <v>08.08.2026</v>
       </c>
     </row>
     <row r="6">
@@ -1042,10 +1042,10 @@
         <v>10</v>
       </c>
       <c r="AZ6" t="str">
-        <v>26.09.2026</v>
+        <v>27.09.2026</v>
       </c>
       <c r="BA6" t="str">
-        <v>07.08.2026</v>
+        <v>08.08.2026</v>
       </c>
     </row>
     <row r="7">
@@ -1203,10 +1203,10 @@
         <v>10</v>
       </c>
       <c r="AZ7" t="str">
-        <v>26.09.2026</v>
+        <v>27.09.2026</v>
       </c>
       <c r="BA7" t="str">
-        <v>07.08.2026</v>
+        <v>08.08.2026</v>
       </c>
     </row>
     <row r="8">
@@ -1364,10 +1364,10 @@
         <v>10</v>
       </c>
       <c r="AZ8" t="str">
-        <v>26.09.2026</v>
+        <v>27.09.2026</v>
       </c>
       <c r="BA8" t="str">
-        <v>07.08.2026</v>
+        <v>08.08.2026</v>
       </c>
     </row>
     <row r="9">
@@ -1525,10 +1525,10 @@
         <v>0</v>
       </c>
       <c r="AZ9" t="str">
-        <v>26.09.2026</v>
+        <v>27.09.2026</v>
       </c>
       <c r="BA9" t="str">
-        <v>07.08.2026</v>
+        <v>08.08.2026</v>
       </c>
     </row>
     <row r="10">
@@ -1686,10 +1686,10 @@
         <v>10</v>
       </c>
       <c r="AZ10" t="str">
-        <v>26.09.2026</v>
+        <v>27.09.2026</v>
       </c>
       <c r="BA10" t="str">
-        <v>07.08.2026</v>
+        <v>08.08.2026</v>
       </c>
     </row>
     <row r="11">
@@ -1847,10 +1847,10 @@
         <v>10</v>
       </c>
       <c r="AZ11" t="str">
-        <v>26.09.2026</v>
+        <v>27.09.2026</v>
       </c>
       <c r="BA11" t="str">
-        <v>07.08.2026</v>
+        <v>08.08.2026</v>
       </c>
     </row>
     <row r="12">
@@ -2008,10 +2008,10 @@
         <v>10</v>
       </c>
       <c r="AZ12" t="str">
-        <v>26.09.2026</v>
+        <v>27.09.2026</v>
       </c>
       <c r="BA12" t="str">
-        <v>07.08.2026</v>
+        <v>08.08.2026</v>
       </c>
     </row>
     <row r="13">
@@ -2169,10 +2169,10 @@
         <v>10</v>
       </c>
       <c r="AZ13" t="str">
-        <v>26.09.2026</v>
+        <v>27.09.2026</v>
       </c>
       <c r="BA13" t="str">
-        <v>19.04.2024</v>
+        <v>20.04.2024</v>
       </c>
     </row>
     <row r="14">
@@ -2330,10 +2330,10 @@
         <v>10</v>
       </c>
       <c r="AZ14" t="str">
-        <v>26.09.2026</v>
+        <v>27.09.2026</v>
       </c>
       <c r="BA14" t="str">
-        <v>20.03.2026</v>
+        <v>21.03.2026</v>
       </c>
     </row>
     <row r="15">
@@ -2491,7 +2491,7 @@
         <v>10</v>
       </c>
       <c r="AZ15" t="str">
-        <v>26.09.2026</v>
+        <v>27.09.2026</v>
       </c>
       <c r="BA15" t="str">
         <v/>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="AZ16" t="str">
-        <v>26.09.2026</v>
+        <v>27.09.2026</v>
       </c>
       <c r="BA16" t="str">
         <v/>
